--- a/results/Int All Data -0.6/Rando_6_permute.xlsx
+++ b/results/Int All Data -0.6/Rando_6_permute.xlsx
@@ -440,477 +440,477 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9019035684925494</v>
+        <v>0.9165079694471271</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9024608710920976</v>
+        <v>0.9165079694471271</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8781849853540957</v>
+        <v>0.9167867205146419</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.896212217956597</v>
+        <v>0.9112947059246075</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8967695205561452</v>
+        <v>0.9102202073572723</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.89569502198881</v>
+        <v>0.904887621616876</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8731704591710499</v>
+        <v>0.9080315026618033</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8731704591710499</v>
+        <v>0.908389668850915</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8683550693984404</v>
+        <v>0.9020619996647804</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8682355476450823</v>
+        <v>0.9007486571262102</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8682355476450823</v>
+        <v>0.9007486571262102</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8662854873853669</v>
+        <v>0.9011068233153219</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8609529016449704</v>
+        <v>0.9011864379724003</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.860236569266747</v>
+        <v>0.9059222130879313</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8635793871866295</v>
+        <v>0.890322130081171</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8611518385199256</v>
+        <v>0.891754794837618</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8593608080388855</v>
+        <v>0.8944211874755569</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8511628927855952</v>
+        <v>0.8932670742511433</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8541874516126458</v>
+        <v>0.893625240440255</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8515611656064681</v>
+        <v>0.8947793536646687</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8562570336257194</v>
+        <v>0.8947793536646687</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8587242898532217</v>
+        <v>0.8976446831775626</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8617885562410708</v>
+        <v>0.8975650685204843</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8582068943499532</v>
+        <v>0.9010673152900048</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.825056468541236</v>
+        <v>0.9017846453456353</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8304289613779122</v>
+        <v>0.9017846453456353</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8308667422241023</v>
+        <v>0.9026999145988139</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8183313246761539</v>
+        <v>0.9002723659321101</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8183313246761539</v>
+        <v>0.8989193158327413</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8216743421315178</v>
+        <v>0.908669018524874</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8216743421315178</v>
+        <v>0.9065998355827634</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8220325083206296</v>
+        <v>0.9016252164959974</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8199629263075561</v>
+        <v>0.9150363952718072</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8090587113200469</v>
+        <v>0.9150363952718072</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8054371423326496</v>
+        <v>0.9161905084962207</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7973982568580344</v>
+        <v>0.9143200628935837</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7973982568580344</v>
+        <v>0.9176231732526678</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7911502023289781</v>
+        <v>0.9173446217206344</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7850216695532799</v>
+        <v>0.9184189207524882</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7866929787454806</v>
+        <v>0.9229954665538627</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7870511449345923</v>
+        <v>0.9190556384736335</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7834297754826763</v>
+        <v>0.9264576066916219</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7834297754826763</v>
+        <v>0.9238708287107613</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7858575236848616</v>
+        <v>0.9242289948998731</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7839870780822246</v>
+        <v>0.9242289948998731</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7753513819827442</v>
+        <v>0.9217214325051281</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7871311586626334</v>
+        <v>0.9217611400659265</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7986720913712877</v>
+        <v>0.9217611400659265</v>
       </c>
     </row>
     <row r="50">
@@ -920,557 +920,557 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8122822070220527</v>
+        <v>0.9159510659185417</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8135955495606229</v>
+        <v>0.9168663351717202</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8129584327685149</v>
+        <v>0.9118522080596372</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8195247463904032</v>
+        <v>0.8495704001085473</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8223104612462189</v>
+        <v>0.8485358086374919</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8245787805987661</v>
+        <v>0.8182110047808702</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.808581023377577</v>
+        <v>0.8379103447174976</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8203606005219848</v>
+        <v>0.8640969822253792</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8066706706786602</v>
+        <v>0.868832557805429</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7679488151583114</v>
+        <v>0.8790204404147146</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7615018237543</v>
+        <v>0.8800550318857699</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7611436575651882</v>
+        <v>0.8787019817864012</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7593528266196294</v>
+        <v>0.8771899019083573</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7600292519015731</v>
+        <v>0.8806520420461166</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7662773064306295</v>
+        <v>0.8785427524722447</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7653223296166525</v>
+        <v>0.8813683744243401</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7644467679242724</v>
+        <v>0.8422510395798581</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7644467679242724</v>
+        <v>0.8502105099328763</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7500405057027241</v>
+        <v>0.8430058823059916</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7521100877157976</v>
+        <v>0.8329772290108628</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7603878171616477</v>
+        <v>0.8263315002673776</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7593133185943124</v>
+        <v>0.8115273642959191</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7512746326551787</v>
+        <v>0.7839519598374982</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7512746326551787</v>
+        <v>0.7839519598374982</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7485284258246802</v>
+        <v>0.7960096894429767</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7444289693593314</v>
+        <v>0.7964103566896266</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7117959390538826</v>
+        <v>0.7944583010750972</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7132286038103296</v>
+        <v>0.7838332362260657</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7122738265318339</v>
+        <v>0.7636969135851737</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7227009521833172</v>
+        <v>0.7565748936475885</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7004944489229075</v>
+        <v>0.7498102417571892</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6983059437629199</v>
+        <v>0.7498102417571892</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6903073644555475</v>
+        <v>0.7398616021901014</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6646393196638226</v>
+        <v>0.7352848568532456</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6801198809172248</v>
+        <v>0.745591064003001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6893525871770518</v>
+        <v>0.7481776424483801</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.668140967826899</v>
+        <v>0.7449928566297659</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6565996360472819</v>
+        <v>0.580249978051097</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6675828670854251</v>
+        <v>0.5802100709548171</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6285044416598159</v>
+        <v>0.5683119697344582</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6066958121493164</v>
+        <v>0.5672773782634027</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6106352411585828</v>
+        <v>0.5314599612103025</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6045063093119218</v>
+        <v>0.5294300867580273</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5942394106520021</v>
+        <v>0.5294300867580273</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5945975768411139</v>
+        <v>0.5196003703378534</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5975022148438436</v>
+        <v>0.5586392877381456</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.595353217709173</v>
+        <v>0.5780151806594248</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5964277162765083</v>
+        <v>0.5778958584415481</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5954725399270498</v>
+        <v>0.5864519398839502</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6158483051456209</v>
+        <v>0.5646046004900591</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6119882912579515</v>
+        <v>0.5739959374575987</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6148133146036028</v>
+        <v>0.5728815317939836</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5785589148462379</v>
+        <v>0.5966372285319775</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5503831081242867</v>
+        <v>0.5841014119130664</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5496278663271903</v>
+        <v>0.5832260497561677</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5444940179262676</v>
+        <v>0.5321760940530444</v>
       </c>
     </row>
     <row r="106">
@@ -1480,507 +1480,507 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5465228947011358</v>
+        <v>0.5361975321451661</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5366955727067387</v>
+        <v>0.5600328435402383</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5341489013576395</v>
+        <v>0.5698230519350951</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5748593274856135</v>
+        <v>0.5921861905484034</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5748593274856135</v>
+        <v>0.5798884197588015</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5556378750269373</v>
+        <v>0.5512778252228812</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5545631769241206</v>
+        <v>0.5316584990142947</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5522952566425362</v>
+        <v>0.5505600960962879</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5332731401297779</v>
+        <v>0.5344444134055918</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5401571142380538</v>
+        <v>0.520240280626701</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5401571142380538</v>
+        <v>0.5258111117318881</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5362160889449361</v>
+        <v>0.5258111117318881</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.508875338212641</v>
+        <v>0.5104115618839342</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5117408672610163</v>
+        <v>0.4814424020879393</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5106264615974012</v>
+        <v>0.4831137112801399</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5061291313821423</v>
+        <v>0.4753936835048008</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5019105522343983</v>
+        <v>0.4346062366810066</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5021493962056333</v>
+        <v>0.4498868633820466</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5040198418082703</v>
+        <v>0.4507249124039236</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.500159428849638</v>
+        <v>0.4498892578078234</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4996420333463696</v>
+        <v>0.4626655146818207</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4994430964714145</v>
+        <v>0.4402602740819372</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4998808773176046</v>
+        <v>0.4353950004389781</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5012337278814919</v>
+        <v>0.4324508544109313</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5007959470353018</v>
+        <v>0.4278314084810561</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5011541132244136</v>
+        <v>0.4658722494033889</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4999602924392015</v>
+        <v>0.4564396085911997</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4999602924392015</v>
+        <v>0.4549672362739542</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4999602924392015</v>
+        <v>0.4566419375693386</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4999602924392015</v>
+        <v>0.4661079008069214</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5005173955032683</v>
+        <v>0.4645158072008365</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5008755616923801</v>
+        <v>0.4645158072008365</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5015122794135253</v>
+        <v>0.4899420149891054</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5004377808461901</v>
+        <v>0.4908175766814855</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5004377808461901</v>
+        <v>0.4525684207165718</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5004377808461901</v>
+        <v>0.4647440757915572</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4998010631250449</v>
+        <v>0.4672510395798581</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4998010631250449</v>
+        <v>0.455313430334182</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5003581661891118</v>
+        <v>0.455313430334182</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.4459623995338851</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5003581661891118</v>
+        <v>0.4504986391680169</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5003581661891118</v>
+        <v>0.4450473298161879</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5003581661891118</v>
+        <v>0.460288049420948</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5000796146570783</v>
+        <v>0.460288049420948</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5000796146570783</v>
+        <v>0.4712710809236098</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.4653023760685125</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4995225115930115</v>
+        <v>0.4785523301753518</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4997214484679666</v>
+        <v>0.4994428969359331</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4994428969359331</v>
+        <v>0.5000796146570783</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4994428969359331</v>
+        <v>0.5000796146570783</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4994428969359331</v>
+        <v>0.5000796146570783</v>
       </c>
     </row>
   </sheetData>
